--- a/output/pdf_financials_xlsx/NAM.xlsx
+++ b/output/pdf_financials_xlsx/NAM.xlsx
@@ -6351,52 +6351,52 @@
         <v>3.790226</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.48539</v>
+        <v>4.128739</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>5.601728</v>
+        <v>7.255566</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.722053</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.137178</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.341775</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.410517</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.301164</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>12.157423</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>12.794361</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.322757</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>14.495175</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>17.12439</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>18.169621</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>18.201968</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>18.202726</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>18.202726</v>
       </c>
     </row>
     <row r="93">
@@ -7906,10 +7906,10 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.890288</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-3.224377</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -10650,7 +10650,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11814,7 +11818,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12436,7 +12444,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -13256,7 +13268,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -14840,7 +14856,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -38440,7 +38460,11 @@
           <t>Exploration and evaluation expenditures 10</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NAM.xlsx
+++ b/output/pdf_financials_xlsx/NAM.xlsx
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.017214</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.017014</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.0177</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2109,13 +2109,13 @@
         <v>-0.631475</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.719401</v>
+        <v>-0.736615</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.182804</v>
+        <v>-1.199818</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.65041</v>
+        <v>-0.66811</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-0.6576610000000001</v>
@@ -2231,13 +2231,13 @@
         <v>-0.631475</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.672841</v>
+        <v>-0.690055</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.144198</v>
+        <v>-1.161212</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.5925280000000001</v>
+        <v>-0.610228</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-0.6056550000000001</v>
@@ -54758,7 +54758,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">

--- a/output/pdf_financials_xlsx/NAM.xlsx
+++ b/output/pdf_financials_xlsx/NAM.xlsx
@@ -2167,7 +2167,7 @@
         <v>0.00512</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.032741</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>0.04656</v>
@@ -2228,7 +2228,7 @@
         <v>-1.301622</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.631475</v>
+        <v>-0.598734</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.690055</v>
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.032741</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>0</v>
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.002178</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -29328,7 +29328,11 @@
           <t>Depreciation – right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -37398,7 +37402,11 @@
           <t>Proceeds from sale of property and equipment 10</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -38676,7 +38684,11 @@
           <t>Proceeds from sale of property and equipment 11</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -55908,7 +55920,11 @@
           <t>Depreciation of right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NAM.xlsx
+++ b/output/pdf_financials_xlsx/NAM.xlsx
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.886256</v>
+        <v>0.931256</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.811814</v>
+        <v>0.837564</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.71791</v>
+        <v>0.74691</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.722741</v>
+        <v>0.745741</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.048206</v>
+        <v>1.077206</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.818737</v>
+        <v>0.845737</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.735052</v>
@@ -949,10 +949,10 @@
         <v>2.627172</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.469429</v>
+        <v>1.498429</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.221285</v>
+        <v>1.248285</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.876928</v>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.46252</v>
+        <v>-0.46252</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.8405280000000001</v>
+        <v>-0.92</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.046145</v>
+        <v>-0.2655</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.162543</v>
@@ -1622,13 +1622,13 @@
         <v>-0.883378</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-5.354466</v>
+        <v>-5.274994</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.771019</v>
+        <v>-3.551664</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-4.316193</v>
+        <v>-4.15365</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-4.987597</v>
@@ -1683,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.079472</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>2.780645</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -2353,10 +2353,10 @@
         <v>-34.36515991553595</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-13.56785817710235</v>
+        <v>-14.85070042037167</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-79.8012608313397</v>
+        <v>-6.955425546295626</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-3.913257014914593</v>
@@ -4495,52 +4495,52 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.010543</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.366246</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.076664</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.044157</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.017403</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.026415</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.017293</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.015589</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.196891</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.17466</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.046039</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.222351</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.1181</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>1.603884</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>0.027665</v>
       </c>
     </row>
     <row r="65">
@@ -4759,46 +4759,46 @@
         <v>0.403338</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.413715</v>
+        <v>0.490379</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.07535500000000001</v>
+        <v>0.119512</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.054693</v>
+        <v>0.07209599999999999</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.038415</v>
+        <v>0.06483</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.042293</v>
+        <v>0.059586</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.060589</v>
+        <v>0.076178</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.243391</v>
+        <v>0.440282</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.20666</v>
+        <v>0.38132</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.063039</v>
+        <v>0.109078</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.0626</v>
+        <v>0.1082</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.276845</v>
+        <v>0.499196</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.241914</v>
+        <v>0.360014</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>1.753609</v>
+        <v>3.357493</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.074001</v>
+        <v>0.101666</v>
       </c>
     </row>
     <row r="69">
@@ -5221,37 +5221,37 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.031329</v>
+        <v>0.004914</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.033478</v>
+        <v>0.016185</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.096914</v>
+        <v>0.08132499999999999</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.032557</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.038441</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.274848</v>
+        <v>0.229248</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.006364</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.047117</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.038679</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>0.055229</v>
+        <v>0.027564</v>
       </c>
     </row>
     <row r="76">
@@ -7412,7 +7412,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.066632</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -40256,7 +40256,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -63092,7 +63096,11 @@
           <t>Director fees 17</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -64142,7 +64150,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
@@ -66446,7 +66458,11 @@
           <t>Director fees (Note 7f)</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr">
         <is>
           <t>-</t>
@@ -68910,7 +68926,11 @@
           <t>Future Income Tax Recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -69014,7 +69034,11 @@
           <t>Loss From Continuing Operations $</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E581" s="5" t="n">
         <v>-0.883378</v>
       </c>
@@ -69114,7 +69138,11 @@
           <t>Gain (Loss) From Discontinued Operation (Note 14) $</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -70350,7 +70378,11 @@
           <t>Director fees (Note 8l)</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E594" s="5" t="n">
         <v>0.045</v>
       </c>
@@ -70966,7 +70998,11 @@
           <t>Future Income Tax Recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E600" s="5" t="n">
         <v>0.46252</v>
       </c>
